--- a/Мастер над Мертвыми/Бусты.xlsx
+++ b/Мастер над Мертвыми/Бусты.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\my_books\Мастер над Мертвыми\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{691B9C56-49AA-4F5D-A02E-A3BEE9B23900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F968D0-9CBE-4030-B441-2EBFF55DF360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="67">
   <si>
     <t>8 глава</t>
   </si>
@@ -164,38 +164,84 @@
     <t>18 глава</t>
   </si>
   <si>
+    <t xml:space="preserve">Великие приключения, обещающие землянам великое могущество. Тем, кто выживет...  https://author.today/reader/118588/942198 </t>
+  </si>
+  <si>
+    <t>Кречет</t>
+  </si>
+  <si>
+    <t>Отдал</t>
+  </si>
+  <si>
+    <t>Писать на АТ</t>
+  </si>
+  <si>
     <t>19 глава</t>
   </si>
   <si>
-    <t>Кречет</t>
-  </si>
-  <si>
-    <t>Писать на АТ</t>
+    <t>Очнулся в госпитале посреди зомби-апокалипсиса. Амнезия. Из прошлого только военный жетон и инстинкты. И инстинкты говорят: выживай. https://author.today/reader/430337</t>
+  </si>
+  <si>
+    <t>Наиль Выборнов</t>
+  </si>
+  <si>
+    <t>Отдает 3.11</t>
+  </si>
+  <si>
+    <t>Профиль тг @etozhenail</t>
   </si>
   <si>
     <t>20 глава</t>
   </si>
   <si>
+    <t>РеалРПГ: Гибель человечества, перенос его остатков в мир Архипелага, классный герой и требование системы построить корабль за две недели.
+Йо-хо-хо! Все на борт! https://author.today/work/415840</t>
+  </si>
+  <si>
+    <t>Артем Сластин</t>
+  </si>
+  <si>
     <t>21 глава</t>
   </si>
   <si>
+    <t>РеалРПГ: Суровый мир, не знающий пощады к попавшему в него герою. Получится ли у него выжить, или он станет ещё одним без вести пропавшим на просторах Эйденвальда? https://author.today/work/125926</t>
+  </si>
+  <si>
+    <t>Мстислав Коган</t>
+  </si>
+  <si>
     <t>22 глава</t>
   </si>
   <si>
+    <t>🔥 Динамичный сюжет в жанре ЛитРПГ и не только. Много приключений. Разные временные и географические локации!
+🌟 Большой квест. Окольцованный https://author.today/reader/405608/3753543</t>
+  </si>
+  <si>
+    <t>Владимир Мельников</t>
+  </si>
+  <si>
+    <t>Профиль тг @UNG1968</t>
+  </si>
+  <si>
     <t>Мёртвые не требуют сна, еды и зарплаты. Главное, чтобы они не начали думать. Некропанк / техно-хоррор. https://author.today/work/497537</t>
   </si>
   <si>
     <t>Написать 29.11 и спросить про буст @etozhenail</t>
   </si>
   <si>
-    <t xml:space="preserve">Великие приключения, обещающие землянам великое могущество. Тем, кто выживет...  https://author.today/reader/118588/942198 </t>
+    <t>Отдает 5.11</t>
+  </si>
+  <si>
+    <t>Инженер. Система против монстров.
+Крафт. Прокачка. Выживание.
+https://author.today/reader/490774/4613251</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -209,6 +255,13 @@
       <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="1"/>
     </font>
     <font>
@@ -230,13 +283,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00A933"/>
-        <bgColor rgb="FF008000"/>
+        <bgColor rgb="FF00B050"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FF00A933"/>
       </patternFill>
     </fill>
   </fills>
@@ -253,7 +306,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
@@ -275,8 +328,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -297,7 +356,7 @@
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF00A933"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
@@ -337,7 +396,7 @@
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF00A933"/>
+      <rgbColor rgb="FF00B050"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
@@ -596,7 +655,7 @@
       <c r="A3" s="2">
         <v>45961</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -605,7 +664,7 @@
       <c r="D3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F3" s="7" t="s">
@@ -616,7 +675,7 @@
       <c r="A4" s="2">
         <v>45962</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -665,12 +724,14 @@
       <c r="D6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="F6" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>45965</v>
       </c>
@@ -683,22 +744,28 @@
       <c r="D7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="47.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>45966</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>33</v>
       </c>
+      <c r="C8" s="12" t="s">
+        <v>66</v>
+      </c>
       <c r="D8" s="7" t="s">
         <v>34</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>35</v>
@@ -717,11 +784,11 @@
       <c r="D9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>45968</v>
       </c>
@@ -746,70 +813,103 @@
         <v>43</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="10" t="s">
-        <v>22</v>
+      <c r="E11" s="9" t="s">
+        <v>46</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>45970</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>45971</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>45972</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>45973</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
+        <v>59</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="17" spans="3:3" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="5" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C20" s="9"/>
+      <c r="C20" s="11"/>
     </row>
     <row r="21" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C21" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -817,7 +917,9 @@
     <hyperlink ref="D4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="C6" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="C9" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="C10" r:id="rId4" display="https://author.today/work/506468" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="C10" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="C13" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D15" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Мастер над Мертвыми/Бусты.xlsx
+++ b/Мастер над Мертвыми/Бусты.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\my_books\Мастер над Мертвыми\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F968D0-9CBE-4030-B441-2EBFF55DF360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE98863-8318-4D5F-A6DA-E48797025E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -111,6 +111,9 @@
     <t>Антон Т</t>
   </si>
   <si>
+    <t>Отдает 5.11</t>
+  </si>
+  <si>
     <t>Профиль тг @AntonTopchiy</t>
   </si>
   <si>
@@ -132,7 +135,15 @@
     <t>15 глава</t>
   </si>
   <si>
+    <t>Инженер. Система против монстров.
+Крафт. Прокачка. Выживание.
+https://author.today/reader/490774/4613251</t>
+  </si>
+  <si>
     <t>Сергей Шиленко</t>
+  </si>
+  <si>
+    <t>Отдает 3.11</t>
   </si>
   <si>
     <t>Профиль тг @Sshilenko</t>
@@ -185,9 +196,6 @@
     <t>Наиль Выборнов</t>
   </si>
   <si>
-    <t>Отдает 3.11</t>
-  </si>
-  <si>
     <t>Профиль тг @etozhenail</t>
   </si>
   <si>
@@ -227,14 +235,6 @@
   </si>
   <si>
     <t>Написать 29.11 и спросить про буст @etozhenail</t>
-  </si>
-  <si>
-    <t>Отдает 5.11</t>
-  </si>
-  <si>
-    <t>Инженер. Система против монстров.
-Крафт. Прокачка. Выживание.
-https://author.today/reader/490774/4613251</t>
   </si>
 </sst>
 </file>
@@ -273,7 +273,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -292,6 +292,12 @@
         <bgColor rgb="FF00A933"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -306,7 +312,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
@@ -329,14 +335,19 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -695,7 +706,7 @@
       <c r="A5" s="2">
         <v>45963</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="9" t="s">
         <v>19</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -715,7 +726,7 @@
       <c r="A6" s="2">
         <v>45964</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="9" t="s">
         <v>24</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -724,65 +735,65 @@
       <c r="D6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>65</v>
+      <c r="E6" s="10" t="s">
+        <v>27</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>45965</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>28</v>
+      <c r="B7" s="9" t="s">
+        <v>29</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="47.85" customHeight="1" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>45966</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>66</v>
+      <c r="B8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>51</v>
+        <v>36</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>45967</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>36</v>
+      <c r="B9" s="15" t="s">
+        <v>39</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>3</v>
@@ -792,17 +803,18 @@
       <c r="A10" s="2">
         <v>45968</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>39</v>
+      <c r="B10" s="15" t="s">
+        <v>42</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>41</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="E10" s="11"/>
       <c r="F10" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -810,19 +822,19 @@
         <v>45969</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -830,19 +842,19 @@
         <v>45970</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -850,16 +862,16 @@
         <v>45971</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>51</v>
+        <v>57</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -867,16 +879,16 @@
         <v>45972</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>51</v>
+        <v>60</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -884,32 +896,32 @@
         <v>45973</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="3:3" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C20" s="11"/>
+      <c r="C20" s="14"/>
     </row>
     <row r="21" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C21" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/Мастер над Мертвыми/Бусты.xlsx
+++ b/Мастер над Мертвыми/Бусты.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\my_books\Мастер над Мертвыми\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE98863-8318-4D5F-A6DA-E48797025E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D58E35-586B-4D31-B5F4-21C36C74C8EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -821,7 +821,7 @@
       <c r="A11" s="2">
         <v>45969</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="15" t="s">
         <v>46</v>
       </c>
       <c r="C11" s="4" t="s">

--- a/Мастер над Мертвыми/Бусты.xlsx
+++ b/Мастер над Мертвыми/Бусты.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\my_books\Мастер над Мертвыми\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D58E35-586B-4D31-B5F4-21C36C74C8EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B49C892-4086-4FD8-9D9A-51A64C9F0086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="66">
   <si>
     <t>8 глава</t>
   </si>
@@ -212,12 +212,6 @@
     <t>21 глава</t>
   </si>
   <si>
-    <t>РеалРПГ: Суровый мир, не знающий пощады к попавшему в него герою. Получится ли у него выжить, или он станет ещё одним без вести пропавшим на просторах Эйденвальда? https://author.today/work/125926</t>
-  </si>
-  <si>
-    <t>Мстислав Коган</t>
-  </si>
-  <si>
     <t>22 глава</t>
   </si>
   <si>
@@ -235,6 +229,9 @@
   </si>
   <si>
     <t>Написать 29.11 и спросить про буст @etozhenail</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> РеалРПГ: Суровый мир, не знающий пощады к попавшему в него герою. Получится ли у него выжить, или он станет ещё одним без вести пропавшим на просторах Эйденвальда? https://author.today/work/125926</t>
   </si>
 </sst>
 </file>
@@ -837,18 +834,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>45970</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="15" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>37</v>
@@ -874,18 +868,18 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>45972</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>60</v>
+        <v>52</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>37</v>
@@ -895,25 +889,25 @@
       <c r="A15" s="2">
         <v>45973</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="13" t="s">
         <v>61</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>63</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>49</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="3:3" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="3:3" x14ac:dyDescent="0.25">
@@ -921,7 +915,7 @@
     </row>
     <row r="21" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C21" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
